--- a/artfynd/S 842-2025 artfynd.xlsx
+++ b/artfynd/S 842-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118490152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119809414</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159964</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159971</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128321285</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104422</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621232</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128385171</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112721329</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128385178</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128385176</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128331635</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128385174</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2492,6 +2572,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129180910</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2615,6 +2700,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128356959</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2729,6 +2819,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6785735</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2834,6 +2929,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72632247</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2939,6 +3039,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6785736</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3036,6 +3141,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133607755</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3133,6 +3243,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133607760</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3258,6 +3373,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133594181</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3383,6 +3503,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133594187</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3484,6 +3609,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851704</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3585,6 +3715,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120851590</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3682,6 +3817,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894664</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3779,6 +3919,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894669</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3876,6 +4021,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894627</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3973,6 +4123,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894631</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4070,6 +4225,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894665</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4167,6 +4327,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120894620</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4268,6 +4433,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283632</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4369,8 +4539,49 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>